--- a/output/yearly_benthic_cover_iteration_28_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_28_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.37661006182049</v>
+        <v>45.2434847772688</v>
       </c>
       <c r="M2" t="n">
-        <v>99.46483463913378</v>
+        <v>100.1517185285959</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.88513670605265</v>
+        <v>88.07559576067652</v>
       </c>
       <c r="C3" t="n">
-        <v>45.86030155054098</v>
+        <v>45.92985026233293</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22841731157819</v>
+        <v>2.228853537248187</v>
       </c>
       <c r="E3" t="n">
-        <v>5.659529735921253</v>
+        <v>5.709734031102877</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428057705260636</v>
+        <v>0.7429511790827291</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95086796923351</v>
+        <v>33.97300676193301</v>
       </c>
       <c r="H3" t="n">
-        <v>34.16906544419891</v>
+        <v>34.17575423780553</v>
       </c>
       <c r="I3" t="n">
-        <v>6.491914408806814</v>
+        <v>6.601851144237131</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642536065787897</v>
+        <v>4.643444869267056</v>
       </c>
       <c r="K3" t="n">
-        <v>12.11486329394736</v>
+        <v>11.92440423932347</v>
       </c>
       <c r="L3" t="n">
-        <v>48.79177595694676</v>
+        <v>48.90878596613896</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7669408014351</v>
+        <v>106.7630404677954</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.83746928934372</v>
+        <v>87.21306513090309</v>
       </c>
       <c r="C4" t="n">
-        <v>42.43560814955104</v>
+        <v>42.70893864962632</v>
       </c>
       <c r="D4" t="n">
-        <v>2.177137642051635</v>
+        <v>2.187584141645732</v>
       </c>
       <c r="E4" t="n">
-        <v>6.432825434420768</v>
+        <v>6.522868608176007</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443515274844492</v>
+        <v>0.7445166900512281</v>
       </c>
       <c r="G4" t="n">
-        <v>33.16960079788443</v>
+        <v>33.34396342981972</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24017026428466</v>
+        <v>34.24776774235649</v>
       </c>
       <c r="I4" t="n">
-        <v>5.421186576439974</v>
+        <v>5.513135206033757</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652197046777808</v>
+        <v>4.653229312820175</v>
       </c>
       <c r="K4" t="n">
-        <v>13.16253071065628</v>
+        <v>12.7869348690969</v>
       </c>
       <c r="L4" t="n">
-        <v>44.22153018399248</v>
+        <v>44.3207417272702</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8196690441998</v>
+        <v>99.81661524599342</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.47723313984241</v>
+        <v>86.12393897729176</v>
       </c>
       <c r="C5" t="n">
-        <v>41.9166218324011</v>
+        <v>42.4755199391416</v>
       </c>
       <c r="D5" t="n">
-        <v>2.109972807482485</v>
+        <v>2.134725938292714</v>
       </c>
       <c r="E5" t="n">
-        <v>6.988643769992656</v>
+        <v>7.132334917172694</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7456651944217754</v>
+        <v>0.7458429224433423</v>
       </c>
       <c r="G5" t="n">
-        <v>32.14631650603083</v>
+        <v>32.53827922046031</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30059894340166</v>
+        <v>34.30877443239374</v>
       </c>
       <c r="I5" t="n">
-        <v>4.525628453376917</v>
+        <v>4.602463281258079</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660407465136096</v>
+        <v>4.661518265270888</v>
       </c>
       <c r="K5" t="n">
-        <v>14.52276686015759</v>
+        <v>13.87606102270822</v>
       </c>
       <c r="L5" t="n">
-        <v>43.41002279142911</v>
+        <v>43.49527639353813</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84941148398779</v>
+        <v>99.84685735538795</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.77804623718889</v>
+        <v>84.82369527044884</v>
       </c>
       <c r="C6" t="n">
-        <v>40.91997088268766</v>
+        <v>41.89017030281194</v>
       </c>
       <c r="D6" t="n">
-        <v>2.026087481011218</v>
+        <v>2.071453068585039</v>
       </c>
       <c r="E6" t="n">
-        <v>7.340303216616116</v>
+        <v>7.561129784430682</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7467857727081391</v>
+        <v>0.7469687531205697</v>
       </c>
       <c r="G6" t="n">
-        <v>30.8682885402702</v>
+        <v>31.57385082958466</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35214554457439</v>
+        <v>34.3605626435462</v>
       </c>
       <c r="I6" t="n">
-        <v>3.777024602582959</v>
+        <v>3.841175484178118</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667411079425869</v>
+        <v>4.668554707003559</v>
       </c>
       <c r="K6" t="n">
-        <v>16.22195376281113</v>
+        <v>15.17630472955119</v>
       </c>
       <c r="L6" t="n">
-        <v>42.73236345301852</v>
+        <v>42.80567876537969</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87428809851731</v>
+        <v>99.87215379774281</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>81.93329818306047</v>
+        <v>83.37414417813025</v>
       </c>
       <c r="C7" t="n">
-        <v>39.66130370683602</v>
+        <v>41.03734793842712</v>
       </c>
       <c r="D7" t="n">
-        <v>1.935670641608112</v>
+        <v>2.001144931933509</v>
       </c>
       <c r="E7" t="n">
-        <v>7.537991812319265</v>
+        <v>7.838674238104641</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477432740487036</v>
+        <v>0.7479259226051237</v>
       </c>
       <c r="G7" t="n">
-        <v>29.49075024848757</v>
+        <v>30.50218830803992</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39619060624035</v>
+        <v>34.40459243983568</v>
       </c>
       <c r="I7" t="n">
-        <v>3.151556137552074</v>
+        <v>3.205081321329357</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673395462804397</v>
+        <v>4.674537016282022</v>
       </c>
       <c r="K7" t="n">
-        <v>18.06670181693951</v>
+        <v>16.62585582186976</v>
       </c>
       <c r="L7" t="n">
-        <v>42.16707712615273</v>
+        <v>42.23009692069819</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89508264992827</v>
+        <v>99.89330068099505</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86.76818042516638</v>
+        <v>88.17769351845416</v>
       </c>
       <c r="C8" t="n">
-        <v>41.924892360052</v>
+        <v>43.29637843684098</v>
       </c>
       <c r="D8" t="n">
-        <v>1.939834508726442</v>
+        <v>2.005401627128794</v>
       </c>
       <c r="E8" t="n">
-        <v>9.343619626179915</v>
+        <v>9.642049416176429</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493517623756109</v>
+        <v>0.7495168581892376</v>
       </c>
       <c r="G8" t="n">
-        <v>29.98227209506981</v>
+        <v>30.99150755596925</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47018106927809</v>
+        <v>34.47777547670492</v>
       </c>
       <c r="I8" t="n">
-        <v>5.599472848688932</v>
+        <v>5.626962220602803</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683448514847568</v>
+        <v>4.684480363682734</v>
       </c>
       <c r="K8" t="n">
-        <v>13.23181957483364</v>
+        <v>11.82230648154583</v>
       </c>
       <c r="L8" t="n">
-        <v>44.65703961362823</v>
+        <v>44.69414780337141</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81375154851386</v>
+        <v>99.81283272175823</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.38157303789899</v>
+        <v>86.18899540895075</v>
       </c>
       <c r="C9" t="n">
-        <v>40.4061751674023</v>
+        <v>42.18129987859955</v>
       </c>
       <c r="D9" t="n">
-        <v>1.831019111990908</v>
+        <v>1.915342382275177</v>
       </c>
       <c r="E9" t="n">
-        <v>9.5986282088381</v>
+        <v>9.991983450042826</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507355964935771</v>
+        <v>0.7508785831466275</v>
       </c>
       <c r="G9" t="n">
-        <v>28.30041066906616</v>
+        <v>29.59973060236128</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53383743870454</v>
+        <v>34.54041482474485</v>
       </c>
       <c r="I9" t="n">
-        <v>4.674844534720851</v>
+        <v>4.697654421713561</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692097478084857</v>
+        <v>4.69299114466642</v>
       </c>
       <c r="K9" t="n">
-        <v>15.61842696210103</v>
+        <v>13.81100459104926</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8198569580331</v>
+        <v>43.85139102422332</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84445908753642</v>
+        <v>99.84369549387213</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>81.67389259814102</v>
+        <v>84.04416513012848</v>
       </c>
       <c r="C10" t="n">
-        <v>38.42239710978645</v>
+        <v>40.76555674201942</v>
       </c>
       <c r="D10" t="n">
-        <v>1.708948741640652</v>
+        <v>1.819193781643799</v>
       </c>
       <c r="E10" t="n">
-        <v>9.609024856581637</v>
+        <v>10.14386076164825</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519311237410534</v>
+        <v>0.7520462408309674</v>
       </c>
       <c r="G10" t="n">
-        <v>26.41367907308574</v>
+        <v>28.11384865100898</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58883169208845</v>
+        <v>34.59412707822448</v>
       </c>
       <c r="I10" t="n">
-        <v>3.901907587621901</v>
+        <v>3.920799611578457</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699569523381584</v>
+        <v>4.700289005193545</v>
       </c>
       <c r="K10" t="n">
-        <v>18.32610740185899</v>
+        <v>15.95583486987152</v>
       </c>
       <c r="L10" t="n">
-        <v>43.12163869572343</v>
+        <v>43.14811798750591</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87014320736887</v>
+        <v>99.86950959939685</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>78.92420285084108</v>
+        <v>81.73644182789874</v>
       </c>
       <c r="C11" t="n">
-        <v>36.27582565714107</v>
+        <v>39.0657816345104</v>
       </c>
       <c r="D11" t="n">
-        <v>1.586588159013145</v>
+        <v>1.716727764444479</v>
       </c>
       <c r="E11" t="n">
-        <v>9.463696370503552</v>
+        <v>10.117790280699</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529651680788194</v>
+        <v>0.7530496545426352</v>
       </c>
       <c r="G11" t="n">
-        <v>24.5224619277336</v>
+        <v>26.53033724695702</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63639773162569</v>
+        <v>34.6402841089612</v>
       </c>
       <c r="I11" t="n">
-        <v>3.256061193393649</v>
+        <v>3.271692431402946</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706032300492621</v>
+        <v>4.706560340891468</v>
       </c>
       <c r="K11" t="n">
-        <v>21.07579714915893</v>
+        <v>18.26355817210123</v>
       </c>
       <c r="L11" t="n">
-        <v>42.53999087182162</v>
+        <v>42.56174909306674</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89161367812162</v>
+        <v>99.89108889967838</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>76.22434760913525</v>
+        <v>79.30830240726401</v>
       </c>
       <c r="C12" t="n">
-        <v>34.07808710492797</v>
+        <v>37.14416725259213</v>
       </c>
       <c r="D12" t="n">
-        <v>1.467913094631733</v>
+        <v>1.60991964986967</v>
       </c>
       <c r="E12" t="n">
-        <v>9.208590166463692</v>
+        <v>9.943223808241369</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538596814940676</v>
+        <v>0.7539135732471847</v>
       </c>
       <c r="G12" t="n">
-        <v>22.6882085132403</v>
+        <v>24.87972300335373</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6775453487271</v>
+        <v>34.68002436937047</v>
       </c>
       <c r="I12" t="n">
-        <v>2.716607795240429</v>
+        <v>2.729538170386695</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711623009337922</v>
+        <v>4.711959832794903</v>
       </c>
       <c r="K12" t="n">
-        <v>23.77565239086476</v>
+        <v>20.69169759273598</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05581435994635</v>
+        <v>42.07325480935512</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90955385573906</v>
+        <v>99.90911965468322</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>73.62488728420065</v>
+        <v>76.83748237687907</v>
       </c>
       <c r="C13" t="n">
-        <v>31.89641776912305</v>
+        <v>35.09506252799181</v>
       </c>
       <c r="D13" t="n">
-        <v>1.354936030217575</v>
+        <v>1.502219753996932</v>
       </c>
       <c r="E13" t="n">
-        <v>8.87755021554562</v>
+        <v>9.657522142876354</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546331375976898</v>
+        <v>0.7546582432589392</v>
       </c>
       <c r="G13" t="n">
-        <v>20.9420239441291</v>
+        <v>23.2153271578712</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71312432949372</v>
+        <v>34.71427918991118</v>
       </c>
       <c r="I13" t="n">
-        <v>2.266162517231398</v>
+        <v>2.276861868596084</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716457109985561</v>
+        <v>4.716614020368368</v>
       </c>
       <c r="K13" t="n">
-        <v>26.37511271579933</v>
+        <v>23.16251762312094</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65300818743204</v>
+        <v>41.66659934415429</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92453867235443</v>
+        <v>99.92417949526704</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>81.60840974753832</v>
+        <v>83.52523287017203</v>
       </c>
       <c r="C14" t="n">
-        <v>36.85752141919126</v>
+        <v>39.23441536515427</v>
       </c>
       <c r="D14" t="n">
-        <v>1.35660251363196</v>
+        <v>1.503993598772128</v>
       </c>
       <c r="E14" t="n">
-        <v>11.60662148879427</v>
+        <v>11.97026315146426</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555612873993818</v>
+        <v>0.7555493556133746</v>
       </c>
       <c r="G14" t="n">
-        <v>23.18406848954397</v>
+        <v>25.05093787568581</v>
       </c>
       <c r="H14" t="n">
-        <v>36.97210643496916</v>
+        <v>36.56346805162119</v>
       </c>
       <c r="I14" t="n">
-        <v>3.011191486953417</v>
+        <v>2.958837364431667</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722258046246136</v>
+        <v>4.722183472583589</v>
       </c>
       <c r="K14" t="n">
-        <v>18.39159025246171</v>
+        <v>16.47476712982798</v>
       </c>
       <c r="L14" t="n">
-        <v>44.65063857946924</v>
+        <v>44.19230591690678</v>
       </c>
       <c r="M14" t="n">
-        <v>99.8997502511222</v>
+        <v>99.90148841188902</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>80.6941670154355</v>
+        <v>82.75576847201451</v>
       </c>
       <c r="C15" t="n">
-        <v>36.40066343904641</v>
+        <v>38.9222292173269</v>
       </c>
       <c r="D15" t="n">
-        <v>1.322967927846356</v>
+        <v>1.475419639320395</v>
       </c>
       <c r="E15" t="n">
-        <v>11.74368566520521</v>
+        <v>12.15420160375323</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563452833748074</v>
+        <v>0.7563004849017959</v>
       </c>
       <c r="G15" t="n">
-        <v>22.61543512354603</v>
+        <v>24.57500201819804</v>
       </c>
       <c r="H15" t="n">
-        <v>37.01664499337015</v>
+        <v>36.59981761837786</v>
       </c>
       <c r="I15" t="n">
-        <v>2.511930001000399</v>
+        <v>2.468149076826956</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727158021092547</v>
+        <v>4.726878030636223</v>
       </c>
       <c r="K15" t="n">
-        <v>19.30583298456451</v>
+        <v>17.24423152798551</v>
       </c>
       <c r="L15" t="n">
-        <v>44.20985936841817</v>
+        <v>43.75134932789783</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91635579202908</v>
+        <v>99.91781007321023</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.04221121186174</v>
+        <v>80.3218882859851</v>
       </c>
       <c r="C16" t="n">
-        <v>34.13535736320428</v>
+        <v>36.8698420430367</v>
       </c>
       <c r="D16" t="n">
-        <v>1.225738522726242</v>
+        <v>1.382606059979536</v>
       </c>
       <c r="E16" t="n">
-        <v>11.22979370146426</v>
+        <v>11.73271388041458</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570221202877503</v>
+        <v>0.7569465856016477</v>
       </c>
       <c r="G16" t="n">
-        <v>20.95335000620351</v>
+        <v>23.02907309138207</v>
       </c>
       <c r="H16" t="n">
-        <v>37.04977038236315</v>
+        <v>36.63108451328241</v>
       </c>
       <c r="I16" t="n">
-        <v>2.095148227018383</v>
+        <v>2.058547995314557</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731388251798439</v>
+        <v>4.730916160010297</v>
       </c>
       <c r="K16" t="n">
-        <v>21.95778878813825</v>
+        <v>19.6781117140149</v>
       </c>
       <c r="L16" t="n">
-        <v>43.83707801529636</v>
+        <v>43.38348654636988</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93022416663889</v>
+        <v>99.93144030342148</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.1282581862765</v>
+        <v>81.94325443702576</v>
       </c>
       <c r="C17" t="n">
-        <v>35.62840960506751</v>
+        <v>38.05171527571514</v>
       </c>
       <c r="D17" t="n">
-        <v>1.226806197150746</v>
+        <v>1.383764054398104</v>
       </c>
       <c r="E17" t="n">
-        <v>12.14595341032004</v>
+        <v>12.48978797997981</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757681521246135</v>
+        <v>0.7575805622249628</v>
       </c>
       <c r="G17" t="n">
-        <v>21.52900245383908</v>
+        <v>23.45245269269145</v>
       </c>
       <c r="H17" t="n">
-        <v>37.63944354978768</v>
+        <v>37.06585640756937</v>
       </c>
       <c r="I17" t="n">
-        <v>2.093861546144477</v>
+        <v>2.058934226256046</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735509507788343</v>
+        <v>4.734878513906017</v>
       </c>
       <c r="K17" t="n">
-        <v>19.8717418137235</v>
+        <v>18.05674556297425</v>
       </c>
       <c r="L17" t="n">
-        <v>44.43011393840706</v>
+        <v>43.82296545398257</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93026535719807</v>
+        <v>99.93142629267194</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.61842018036955</v>
+        <v>79.69464967774179</v>
       </c>
       <c r="C18" t="n">
-        <v>33.44041968028021</v>
+        <v>36.1209436169904</v>
       </c>
       <c r="D18" t="n">
-        <v>1.139438555611299</v>
+        <v>1.301336811155375</v>
       </c>
       <c r="E18" t="n">
-        <v>11.57200520620018</v>
+        <v>12.03197209114026</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582497103675749</v>
+        <v>0.7581246280055807</v>
       </c>
       <c r="G18" t="n">
-        <v>19.99580334426712</v>
+        <v>22.05545078575874</v>
       </c>
       <c r="H18" t="n">
-        <v>37.66766955472821</v>
+        <v>37.09247570735899</v>
       </c>
       <c r="I18" t="n">
-        <v>1.746193119397824</v>
+        <v>1.717010729287963</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739060689797343</v>
+        <v>4.738278925034877</v>
       </c>
       <c r="K18" t="n">
-        <v>22.38157981963046</v>
+        <v>20.30535032225819</v>
       </c>
       <c r="L18" t="n">
-        <v>44.11983767936309</v>
+        <v>43.51651344335543</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94183717927375</v>
+        <v>99.94280738260403</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.72661038330877</v>
+        <v>78.81136145075394</v>
       </c>
       <c r="C19" t="n">
-        <v>32.80560414862574</v>
+        <v>35.50206980147317</v>
       </c>
       <c r="D19" t="n">
-        <v>1.108646720239429</v>
+        <v>1.269624349991149</v>
       </c>
       <c r="E19" t="n">
-        <v>11.50368056887884</v>
+        <v>11.9773813765471</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758732753778818</v>
+        <v>0.7585837046383965</v>
       </c>
       <c r="G19" t="n">
-        <v>19.45544293459621</v>
+        <v>21.5179783800701</v>
       </c>
       <c r="H19" t="n">
-        <v>37.69166576514084</v>
+        <v>37.11493677539649</v>
       </c>
       <c r="I19" t="n">
-        <v>1.466361929557025</v>
+        <v>1.431708710120713</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742079711117612</v>
+        <v>4.741148153989977</v>
       </c>
       <c r="K19" t="n">
-        <v>23.27338961669123</v>
+        <v>21.18863854924608</v>
       </c>
       <c r="L19" t="n">
-        <v>43.87215862209732</v>
+        <v>43.2615969068005</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9511523874143</v>
+        <v>99.95230525751974</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.07310341836234</v>
+        <v>76.42142429196662</v>
       </c>
       <c r="C20" t="n">
-        <v>30.37665739165198</v>
+        <v>33.33247908442065</v>
       </c>
       <c r="D20" t="n">
-        <v>1.017469195755703</v>
+        <v>1.182958966260873</v>
       </c>
       <c r="E20" t="n">
-        <v>10.76136621941937</v>
+        <v>11.35874950174557</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591502051088839</v>
+        <v>0.7589786769153331</v>
       </c>
       <c r="G20" t="n">
-        <v>17.85538487089871</v>
+        <v>20.04914718332946</v>
       </c>
       <c r="H20" t="n">
-        <v>37.71240354919944</v>
+        <v>37.13426143396336</v>
       </c>
       <c r="I20" t="n">
-        <v>1.222640596049697</v>
+        <v>1.193711799031193</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744688781930524</v>
+        <v>4.74361673072083</v>
       </c>
       <c r="K20" t="n">
-        <v>25.92689658163768</v>
+        <v>23.57857570803339</v>
       </c>
       <c r="L20" t="n">
-        <v>43.6557137508893</v>
+        <v>43.04917552115372</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95926772417896</v>
+        <v>99.96023031360775</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.73470337814388</v>
+        <v>82.05287638568196</v>
       </c>
       <c r="C21" t="n">
-        <v>34.564664790787</v>
+        <v>36.81215861911548</v>
       </c>
       <c r="D21" t="n">
-        <v>1.018189292417282</v>
+        <v>1.183784944214227</v>
       </c>
       <c r="E21" t="n">
-        <v>12.99895218763868</v>
+        <v>13.24228096076534</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596874808619157</v>
+        <v>0.7595086189269137</v>
       </c>
       <c r="G21" t="n">
-        <v>19.81229838837044</v>
+        <v>21.65228746472727</v>
       </c>
       <c r="H21" t="n">
-        <v>39.68337053671117</v>
+        <v>38.74933106211286</v>
       </c>
       <c r="I21" t="n">
-        <v>1.714158736757416</v>
+        <v>1.718754466642137</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748046755386973</v>
+        <v>4.746928868293208</v>
       </c>
       <c r="K21" t="n">
-        <v>19.26529662185616</v>
+        <v>17.94712361431805</v>
       </c>
       <c r="L21" t="n">
-        <v>46.11294037309634</v>
+        <v>45.18346592598928</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94290178573948</v>
+        <v>99.94274815942282</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_28_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_28_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.2434847772688</v>
+        <v>45.2766846507998</v>
       </c>
       <c r="M2" t="n">
-        <v>100.1517185285959</v>
+        <v>99.84963637532044</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.07559576067652</v>
+        <v>87.94782129696881</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92985026233293</v>
+        <v>45.84966301880392</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228853537248187</v>
+        <v>2.228586522600206</v>
       </c>
       <c r="E3" t="n">
-        <v>5.709734031102877</v>
+        <v>5.657034229544596</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429511790827291</v>
+        <v>0.7428621742000686</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97300676193301</v>
+        <v>33.94649251926657</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17575423780553</v>
+        <v>34.17166001320315</v>
       </c>
       <c r="I3" t="n">
-        <v>6.601851144237131</v>
+        <v>6.558297249403788</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643444869267056</v>
+        <v>4.642888588750428</v>
       </c>
       <c r="K3" t="n">
-        <v>11.92440423932347</v>
+        <v>12.0521787030312</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90878596613896</v>
+        <v>48.86273381757892</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7630404677954</v>
+        <v>106.764575539414</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.21306513090309</v>
+        <v>87.02921509419392</v>
       </c>
       <c r="C4" t="n">
-        <v>42.70893864962632</v>
+        <v>42.56724386080931</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187584141645732</v>
+        <v>2.184220346041216</v>
       </c>
       <c r="E4" t="n">
-        <v>6.522868608176007</v>
+        <v>6.457200638577019</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445166900512281</v>
+        <v>0.7444204410052508</v>
       </c>
       <c r="G4" t="n">
-        <v>33.34396342981972</v>
+        <v>33.27069372689525</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24776774235649</v>
+        <v>34.24334028624153</v>
       </c>
       <c r="I4" t="n">
-        <v>5.513135206033757</v>
+        <v>5.476711899150835</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653229312820175</v>
+        <v>4.652627756282817</v>
       </c>
       <c r="K4" t="n">
-        <v>12.7869348690969</v>
+        <v>12.97078490580607</v>
       </c>
       <c r="L4" t="n">
-        <v>44.3207417272702</v>
+        <v>44.27979630979007</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81661524599342</v>
+        <v>99.81782507640546</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.12393897729176</v>
+        <v>85.90621248923435</v>
       </c>
       <c r="C5" t="n">
-        <v>42.4755199391416</v>
+        <v>42.29418697799676</v>
       </c>
       <c r="D5" t="n">
-        <v>2.134725938292714</v>
+        <v>2.129466918454658</v>
       </c>
       <c r="E5" t="n">
-        <v>7.132334917172694</v>
+        <v>7.057337189835517</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458429224433423</v>
+        <v>0.745741070171754</v>
       </c>
       <c r="G5" t="n">
-        <v>32.53827922046031</v>
+        <v>32.43667323851742</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30877443239374</v>
+        <v>34.30408922790068</v>
       </c>
       <c r="I5" t="n">
-        <v>4.602463281258079</v>
+        <v>4.572023155780855</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661518265270888</v>
+        <v>4.660881688573461</v>
       </c>
       <c r="K5" t="n">
-        <v>13.87606102270822</v>
+        <v>14.09378751076567</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49527639353813</v>
+        <v>43.45989462515005</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84685735538795</v>
+        <v>99.84786911391247</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.82369527044884</v>
+        <v>84.46089174852904</v>
       </c>
       <c r="C6" t="n">
-        <v>41.89017030281194</v>
+        <v>41.55890089235473</v>
       </c>
       <c r="D6" t="n">
-        <v>2.071453068585039</v>
+        <v>2.058619436522306</v>
       </c>
       <c r="E6" t="n">
-        <v>7.561129784430682</v>
+        <v>7.45849867620009</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469687531205697</v>
+        <v>0.7468641014269609</v>
       </c>
       <c r="G6" t="n">
-        <v>31.57385082958466</v>
+        <v>31.35750332923367</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3605626435462</v>
+        <v>34.3557486656402</v>
       </c>
       <c r="I6" t="n">
-        <v>3.841175484178118</v>
+        <v>3.815756905587307</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668554707003559</v>
+        <v>4.667900633918505</v>
       </c>
       <c r="K6" t="n">
-        <v>15.17630472955119</v>
+        <v>15.53910825147097</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80567876537969</v>
+        <v>42.77499021295818</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87215379774281</v>
+        <v>99.87299935678388</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.37414417813025</v>
+        <v>82.86300222136292</v>
       </c>
       <c r="C7" t="n">
-        <v>41.03734793842712</v>
+        <v>40.55356225310403</v>
       </c>
       <c r="D7" t="n">
-        <v>2.001144931933509</v>
+        <v>1.980676496712849</v>
       </c>
       <c r="E7" t="n">
-        <v>7.838674238104641</v>
+        <v>7.706751849817211</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479259226051237</v>
+        <v>0.7478206675527951</v>
       </c>
       <c r="G7" t="n">
-        <v>30.50218830803992</v>
+        <v>30.17025329593262</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40459243983568</v>
+        <v>34.39975070742857</v>
       </c>
       <c r="I7" t="n">
-        <v>3.205081321329357</v>
+        <v>3.183870031713911</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674537016282022</v>
+        <v>4.673879172204968</v>
       </c>
       <c r="K7" t="n">
-        <v>16.62585582186976</v>
+        <v>17.13699777863708</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23009692069819</v>
+        <v>42.20344672088146</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89330068099505</v>
+        <v>99.89400675262257</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.17769351845416</v>
+        <v>87.68939653023877</v>
       </c>
       <c r="C8" t="n">
-        <v>43.29637843684098</v>
+        <v>42.82908193634671</v>
       </c>
       <c r="D8" t="n">
-        <v>2.005401627128794</v>
+        <v>1.984901821288822</v>
       </c>
       <c r="E8" t="n">
-        <v>9.642049416176429</v>
+        <v>9.520516980584537</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495168581892376</v>
+        <v>0.7494159735254137</v>
       </c>
       <c r="G8" t="n">
-        <v>30.99150755596925</v>
+        <v>30.66561330416837</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47777547670492</v>
+        <v>34.47313478216903</v>
       </c>
       <c r="I8" t="n">
-        <v>5.626962220602803</v>
+        <v>5.611963833968752</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684480363682734</v>
+        <v>4.683849834533834</v>
       </c>
       <c r="K8" t="n">
-        <v>11.82230648154583</v>
+        <v>12.31060346976124</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69414780337141</v>
+        <v>44.67364734504501</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81283272175823</v>
+        <v>99.81333275115296</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.18899540895075</v>
+        <v>85.60390283073427</v>
       </c>
       <c r="C9" t="n">
-        <v>42.18129987859955</v>
+        <v>41.61439380144718</v>
       </c>
       <c r="D9" t="n">
-        <v>1.915342382275177</v>
+        <v>1.890184112797893</v>
       </c>
       <c r="E9" t="n">
-        <v>9.991983450042826</v>
+        <v>9.847067973684503</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508785831466275</v>
+        <v>0.7507831775573552</v>
       </c>
       <c r="G9" t="n">
-        <v>29.59973060236128</v>
+        <v>29.20227814547836</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54041482474485</v>
+        <v>34.53602616763835</v>
       </c>
       <c r="I9" t="n">
-        <v>4.697654421713561</v>
+        <v>4.68516839384433</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69299114466642</v>
+        <v>4.692394859733469</v>
       </c>
       <c r="K9" t="n">
-        <v>13.81100459104926</v>
+        <v>14.39609716926574</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85139102422332</v>
+        <v>43.83362114501016</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84369549387213</v>
+        <v>99.84411211572308</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.04416513012848</v>
+        <v>83.36695154587082</v>
       </c>
       <c r="C10" t="n">
-        <v>40.76555674201942</v>
+        <v>40.10407995713305</v>
       </c>
       <c r="D10" t="n">
-        <v>1.819193781643799</v>
+        <v>1.789697628507905</v>
       </c>
       <c r="E10" t="n">
-        <v>10.14386076164825</v>
+        <v>9.975310707228175</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520462408309674</v>
+        <v>0.7519570524663556</v>
       </c>
       <c r="G10" t="n">
-        <v>28.11384865100898</v>
+        <v>27.64981865529998</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59412707822448</v>
+        <v>34.59002441345236</v>
       </c>
       <c r="I10" t="n">
-        <v>3.920799611578457</v>
+        <v>3.910411511001316</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700289005193545</v>
+        <v>4.699731577914722</v>
       </c>
       <c r="K10" t="n">
-        <v>15.95583486987152</v>
+        <v>16.63304845412918</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14811798750591</v>
+        <v>43.13272802224209</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86950959939685</v>
+        <v>99.86985643350432</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.73644182789874</v>
+        <v>81.05066877826503</v>
       </c>
       <c r="C11" t="n">
-        <v>39.0657816345104</v>
+        <v>38.39361398575794</v>
       </c>
       <c r="D11" t="n">
-        <v>1.716727764444479</v>
+        <v>1.686783442649508</v>
       </c>
       <c r="E11" t="n">
-        <v>10.117790280699</v>
+        <v>9.945535265534188</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530496545426352</v>
+        <v>0.7529661631855782</v>
       </c>
       <c r="G11" t="n">
-        <v>26.53033724695702</v>
+        <v>26.05985254554161</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6402841089612</v>
+        <v>34.6364435065366</v>
       </c>
       <c r="I11" t="n">
-        <v>3.271692431402946</v>
+        <v>3.263049334907683</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706560340891468</v>
+        <v>4.706038519909863</v>
       </c>
       <c r="K11" t="n">
-        <v>18.26355817210123</v>
+        <v>18.94933122173496</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56174909306674</v>
+        <v>42.54843225053484</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89108889967838</v>
+        <v>99.89137745802775</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.30830240726401</v>
+        <v>78.49891558220318</v>
       </c>
       <c r="C12" t="n">
-        <v>37.14416725259213</v>
+        <v>36.34658551736398</v>
       </c>
       <c r="D12" t="n">
-        <v>1.60991964986967</v>
+        <v>1.574406425987109</v>
       </c>
       <c r="E12" t="n">
-        <v>9.943223808241369</v>
+        <v>9.73666824661913</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539135732471847</v>
+        <v>0.7538365948842282</v>
       </c>
       <c r="G12" t="n">
-        <v>24.87972300335373</v>
+        <v>24.32369103856712</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68002436937047</v>
+        <v>34.6764833646745</v>
       </c>
       <c r="I12" t="n">
-        <v>2.729538170386695</v>
+        <v>2.722351193444668</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711959832794903</v>
+        <v>4.711478718026425</v>
       </c>
       <c r="K12" t="n">
-        <v>20.69169759273598</v>
+        <v>21.50108441779683</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07325480935512</v>
+        <v>42.0616898055362</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90911965468322</v>
+        <v>99.909359740697</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.83748237687907</v>
+        <v>76.10286887203435</v>
       </c>
       <c r="C13" t="n">
-        <v>35.09506252799181</v>
+        <v>34.37065992831162</v>
       </c>
       <c r="D13" t="n">
-        <v>1.502219753996932</v>
+        <v>1.470005576650844</v>
       </c>
       <c r="E13" t="n">
-        <v>9.657522142876354</v>
+        <v>9.469498074351343</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546582432589392</v>
+        <v>0.7545864020650533</v>
       </c>
       <c r="G13" t="n">
-        <v>23.2153271578712</v>
+        <v>22.71075681681612</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71427918991118</v>
+        <v>34.71097449499245</v>
       </c>
       <c r="I13" t="n">
-        <v>2.276861868596084</v>
+        <v>2.270882494251955</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716614020368368</v>
+        <v>4.716165012906583</v>
       </c>
       <c r="K13" t="n">
-        <v>23.16251762312094</v>
+        <v>23.89713112796566</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66659934415429</v>
+        <v>41.65658807723815</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92417949526704</v>
+        <v>99.92437913351543</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.52523287017203</v>
+        <v>83.06245663734414</v>
       </c>
       <c r="C14" t="n">
-        <v>39.23441536515427</v>
+        <v>38.69676966335008</v>
       </c>
       <c r="D14" t="n">
-        <v>1.503993598772128</v>
+        <v>1.471741731830382</v>
       </c>
       <c r="E14" t="n">
-        <v>11.97026315146426</v>
+        <v>11.874430955248</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555493556133746</v>
+        <v>0.7554776089496822</v>
       </c>
       <c r="G14" t="n">
-        <v>25.05093787568581</v>
+        <v>24.6408223212084</v>
       </c>
       <c r="H14" t="n">
-        <v>36.56346805162119</v>
+        <v>36.65521289805157</v>
       </c>
       <c r="I14" t="n">
-        <v>2.958837364431667</v>
+        <v>2.9430360661206</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722183472583589</v>
+        <v>4.721735055935513</v>
       </c>
       <c r="K14" t="n">
-        <v>16.47476712982798</v>
+        <v>16.93754336265584</v>
       </c>
       <c r="L14" t="n">
-        <v>44.19230591690678</v>
+        <v>44.26770149787612</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90148841188902</v>
+        <v>99.90201452388204</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.75576847201451</v>
+        <v>82.22461351158584</v>
       </c>
       <c r="C15" t="n">
-        <v>38.9222292173269</v>
+        <v>38.31338450066157</v>
       </c>
       <c r="D15" t="n">
-        <v>1.475419639320395</v>
+        <v>1.440713334969815</v>
       </c>
       <c r="E15" t="n">
-        <v>12.15420160375323</v>
+        <v>12.03324683703936</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563004849017959</v>
+        <v>0.7562294825697365</v>
       </c>
       <c r="G15" t="n">
-        <v>24.57500201819804</v>
+        <v>24.12132545744664</v>
       </c>
       <c r="H15" t="n">
-        <v>36.59981761837786</v>
+        <v>36.69169324808317</v>
       </c>
       <c r="I15" t="n">
-        <v>2.468149076826956</v>
+        <v>2.454970885416284</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726878030636223</v>
+        <v>4.726434266060853</v>
       </c>
       <c r="K15" t="n">
-        <v>17.24423152798551</v>
+        <v>17.77538648841416</v>
       </c>
       <c r="L15" t="n">
-        <v>43.75134932789783</v>
+        <v>43.82947800908758</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91781007321023</v>
+        <v>99.91824899816331</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.3218882859851</v>
+        <v>79.75355453999663</v>
       </c>
       <c r="C16" t="n">
-        <v>36.8698420430367</v>
+        <v>36.22142431896636</v>
       </c>
       <c r="D16" t="n">
-        <v>1.382606059979536</v>
+        <v>1.347170184658147</v>
       </c>
       <c r="E16" t="n">
-        <v>11.73271388041458</v>
+        <v>11.59320786023038</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569465856016477</v>
+        <v>0.7568766533581883</v>
       </c>
       <c r="G16" t="n">
-        <v>23.02907309138207</v>
+        <v>22.55516741738806</v>
       </c>
       <c r="H16" t="n">
-        <v>36.63108451328241</v>
+        <v>36.72309349443207</v>
       </c>
       <c r="I16" t="n">
-        <v>2.058547995314557</v>
+        <v>2.047559846441099</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730916160010297</v>
+        <v>4.730479083488676</v>
       </c>
       <c r="K16" t="n">
-        <v>19.6781117140149</v>
+        <v>20.24644546000338</v>
       </c>
       <c r="L16" t="n">
-        <v>43.38348654636988</v>
+        <v>43.46393658532426</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93144030342148</v>
+        <v>99.931806364294</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.94325443702576</v>
+        <v>81.44874811839665</v>
       </c>
       <c r="C17" t="n">
-        <v>38.05171527571514</v>
+        <v>37.45933983722873</v>
       </c>
       <c r="D17" t="n">
-        <v>1.383764054398104</v>
+        <v>1.348292582171738</v>
       </c>
       <c r="E17" t="n">
-        <v>12.48978797997981</v>
+        <v>12.37647636356056</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575805622249628</v>
+        <v>0.7575072466443961</v>
       </c>
       <c r="G17" t="n">
-        <v>23.45245269269145</v>
+        <v>23.00827296819729</v>
       </c>
       <c r="H17" t="n">
-        <v>37.06585640756937</v>
+        <v>37.18800308097689</v>
       </c>
       <c r="I17" t="n">
-        <v>2.058934226256046</v>
+        <v>2.035775585318299</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734878513906017</v>
+        <v>4.734420291527474</v>
       </c>
       <c r="K17" t="n">
-        <v>18.05674556297425</v>
+        <v>18.55125188160337</v>
       </c>
       <c r="L17" t="n">
-        <v>43.82296545398257</v>
+        <v>43.92160558494157</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93142629267194</v>
+        <v>99.93219730377366</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.69464967774179</v>
+        <v>79.04633294628833</v>
       </c>
       <c r="C18" t="n">
-        <v>36.1209436169904</v>
+        <v>35.37088059753768</v>
       </c>
       <c r="D18" t="n">
-        <v>1.301336811155375</v>
+        <v>1.26101364502374</v>
       </c>
       <c r="E18" t="n">
-        <v>12.03197209114026</v>
+        <v>11.85825974309748</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581246280055807</v>
+        <v>0.7580495512197684</v>
       </c>
       <c r="G18" t="n">
-        <v>22.05545078575874</v>
+        <v>21.51887991150577</v>
       </c>
       <c r="H18" t="n">
-        <v>37.09247570735899</v>
+        <v>37.21462622459579</v>
       </c>
       <c r="I18" t="n">
-        <v>1.717010729287963</v>
+        <v>1.69769417572224</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738278925034877</v>
+        <v>4.737809695123551</v>
       </c>
       <c r="K18" t="n">
-        <v>20.30535032225819</v>
+        <v>20.95366705371165</v>
       </c>
       <c r="L18" t="n">
-        <v>43.51651344335543</v>
+        <v>43.61890302693628</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94280738260403</v>
+        <v>99.94345067818563</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.81136145075394</v>
+        <v>78.08171673948063</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50206980147317</v>
+        <v>34.66737750177826</v>
       </c>
       <c r="D19" t="n">
-        <v>1.269624349991149</v>
+        <v>1.226637305800535</v>
       </c>
       <c r="E19" t="n">
-        <v>11.9773813765471</v>
+        <v>11.77092652196216</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585837046383965</v>
+        <v>0.758507658902239</v>
       </c>
       <c r="G19" t="n">
-        <v>21.5179783800701</v>
+        <v>20.93225635000782</v>
       </c>
       <c r="H19" t="n">
-        <v>37.11493677539649</v>
+        <v>37.2371159235163</v>
       </c>
       <c r="I19" t="n">
-        <v>1.431708710120713</v>
+        <v>1.415600111152582</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741148153989977</v>
+        <v>4.740672868138993</v>
       </c>
       <c r="K19" t="n">
-        <v>21.18863854924608</v>
+        <v>21.91828326051935</v>
       </c>
       <c r="L19" t="n">
-        <v>43.2615969068005</v>
+        <v>43.36718106615454</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95230525751974</v>
+        <v>99.95284182845216</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.42142429196662</v>
+        <v>75.59066938463295</v>
       </c>
       <c r="C20" t="n">
-        <v>33.33247908442065</v>
+        <v>32.39389160837403</v>
       </c>
       <c r="D20" t="n">
-        <v>1.182958966260873</v>
+        <v>1.13717204480645</v>
       </c>
       <c r="E20" t="n">
-        <v>11.35874950174557</v>
+        <v>11.10912295138101</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589786769153331</v>
+        <v>0.7589024395406262</v>
       </c>
       <c r="G20" t="n">
-        <v>20.04914718332946</v>
+        <v>19.40555422812319</v>
       </c>
       <c r="H20" t="n">
-        <v>37.13426143396336</v>
+        <v>37.25649673295632</v>
       </c>
       <c r="I20" t="n">
-        <v>1.193711799031193</v>
+        <v>1.180280740696448</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74361673072083</v>
+        <v>4.743140247128912</v>
       </c>
       <c r="K20" t="n">
-        <v>23.57857570803339</v>
+        <v>24.40933061536704</v>
       </c>
       <c r="L20" t="n">
-        <v>43.04917552115372</v>
+        <v>43.15745555094911</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96023031360775</v>
+        <v>99.96067777469018</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.05287638568196</v>
+        <v>81.54236757947359</v>
       </c>
       <c r="C21" t="n">
-        <v>36.81215861911548</v>
+        <v>36.09372882856055</v>
       </c>
       <c r="D21" t="n">
-        <v>1.183784944214227</v>
+        <v>1.137959186748384</v>
       </c>
       <c r="E21" t="n">
-        <v>13.24228096076534</v>
+        <v>13.10068338452312</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595086189269137</v>
+        <v>0.7594277461050344</v>
       </c>
       <c r="G21" t="n">
-        <v>21.65228746472727</v>
+        <v>21.12064231898293</v>
       </c>
       <c r="H21" t="n">
-        <v>38.74933106211286</v>
+        <v>38.98394111204244</v>
       </c>
       <c r="I21" t="n">
-        <v>1.718754466642137</v>
+        <v>1.693290417915227</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746928868293208</v>
+        <v>4.746423413156463</v>
       </c>
       <c r="K21" t="n">
-        <v>17.94712361431805</v>
+        <v>18.45763242052639</v>
       </c>
       <c r="L21" t="n">
-        <v>45.18346592598928</v>
+        <v>45.39223477938769</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94274815942282</v>
+        <v>99.94359602847463</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_28_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_28_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.2766846507998</v>
+        <v>44.08336345886399</v>
       </c>
       <c r="M2" t="n">
-        <v>99.84963637532044</v>
+        <v>94.9866273854187</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.94782129696881</v>
+        <v>81.52577172949734</v>
       </c>
       <c r="C3" t="n">
-        <v>45.84966301880392</v>
+        <v>43.2813272850529</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228586522600206</v>
+        <v>2.18310191919592</v>
       </c>
       <c r="E3" t="n">
-        <v>5.657034229544596</v>
+        <v>4.150772262280041</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428621742000686</v>
+        <v>0.7376674516130525</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94649251926657</v>
+        <v>32.83749136790529</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17166001320315</v>
+        <v>33.93270277420041</v>
       </c>
       <c r="I3" t="n">
-        <v>6.558297249403788</v>
+        <v>3.073614381721052</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642888588750428</v>
+        <v>4.610421572581577</v>
       </c>
       <c r="K3" t="n">
-        <v>12.0521787030312</v>
+        <v>18.47422827050266</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86273381757892</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.764575539414</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.02921509419392</v>
+        <v>88.68123714645476</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56724386080931</v>
+        <v>42.88429582732003</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184220346041216</v>
+        <v>2.188877485987856</v>
       </c>
       <c r="E4" t="n">
-        <v>6.457200638577019</v>
+        <v>6.541531441863765</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444204410052508</v>
+        <v>0.7396190085236882</v>
       </c>
       <c r="G4" t="n">
-        <v>33.27069372689525</v>
+        <v>33.5277216480497</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24334028624153</v>
+        <v>34.02247439208965</v>
       </c>
       <c r="I4" t="n">
-        <v>5.476711899150835</v>
+        <v>7.038394366667055</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652627756282817</v>
+        <v>4.622618803273051</v>
       </c>
       <c r="K4" t="n">
-        <v>12.97078490580607</v>
+        <v>11.31876285354523</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27979630979007</v>
+        <v>45.5629472232524</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81782507640546</v>
+        <v>99.76600590411766</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.90621248923435</v>
+        <v>87.67978025119987</v>
       </c>
       <c r="C5" t="n">
-        <v>42.29418697799676</v>
+        <v>42.9738474623183</v>
       </c>
       <c r="D5" t="n">
-        <v>2.129466918454658</v>
+        <v>2.141780043021406</v>
       </c>
       <c r="E5" t="n">
-        <v>7.057337189835517</v>
+        <v>7.38051862921261</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745741070171754</v>
+        <v>0.7412719184648857</v>
       </c>
       <c r="G5" t="n">
-        <v>32.43667323851742</v>
+        <v>32.80631537098646</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30408922790068</v>
+        <v>34.09850824938474</v>
       </c>
       <c r="I5" t="n">
-        <v>4.572023155780855</v>
+        <v>5.878436549724227</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660881688573461</v>
+        <v>4.632949490405535</v>
       </c>
       <c r="K5" t="n">
-        <v>14.09378751076567</v>
+        <v>12.32021974880014</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45989462515005</v>
+        <v>44.51042183425191</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84786911391247</v>
+        <v>99.80448904537035</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.46089174852904</v>
+        <v>86.49592003248003</v>
       </c>
       <c r="C6" t="n">
-        <v>41.55890089235473</v>
+        <v>42.70247526376055</v>
       </c>
       <c r="D6" t="n">
-        <v>2.058619436522306</v>
+        <v>2.085815726624383</v>
       </c>
       <c r="E6" t="n">
-        <v>7.45849867620009</v>
+        <v>8.00566079936956</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468641014269609</v>
+        <v>0.7426739633272048</v>
       </c>
       <c r="G6" t="n">
-        <v>31.35750332923367</v>
+        <v>31.94909241794578</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3557486656402</v>
+        <v>34.16300231305141</v>
       </c>
       <c r="I6" t="n">
-        <v>3.815756905587307</v>
+        <v>4.907962541366659</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667900633918505</v>
+        <v>4.641712270795029</v>
       </c>
       <c r="K6" t="n">
-        <v>15.53910825147097</v>
+        <v>13.50407996751998</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77499021295818</v>
+        <v>43.63015486456046</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87299935678388</v>
+        <v>99.83671009584098</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.86300222136292</v>
+        <v>85.03302261286606</v>
       </c>
       <c r="C7" t="n">
-        <v>40.55356225310403</v>
+        <v>42.00200695173167</v>
       </c>
       <c r="D7" t="n">
-        <v>1.980676496712849</v>
+        <v>2.016467990011594</v>
       </c>
       <c r="E7" t="n">
-        <v>7.706751849817211</v>
+        <v>8.422250328420727</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478206675527951</v>
+        <v>0.7438665945576244</v>
       </c>
       <c r="G7" t="n">
-        <v>30.17025329593262</v>
+        <v>30.88687142798181</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39975070742857</v>
+        <v>34.21786334965071</v>
       </c>
       <c r="I7" t="n">
-        <v>3.183870031713911</v>
+        <v>4.096536706258446</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673879172204968</v>
+        <v>4.649166215985152</v>
       </c>
       <c r="K7" t="n">
-        <v>17.13699777863708</v>
+        <v>14.96697738713395</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20344672088146</v>
+        <v>42.89468336831865</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89400675262257</v>
+        <v>99.86366770718426</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.68939653023877</v>
+        <v>83.36549217524625</v>
       </c>
       <c r="C8" t="n">
-        <v>42.82908193634671</v>
+        <v>40.97088933477674</v>
       </c>
       <c r="D8" t="n">
-        <v>1.984901821288822</v>
+        <v>1.93774640945707</v>
       </c>
       <c r="E8" t="n">
-        <v>9.520516980584537</v>
+        <v>8.663192349497972</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494159735254137</v>
+        <v>0.7448833495134023</v>
       </c>
       <c r="G8" t="n">
-        <v>30.66561330416837</v>
+        <v>29.68106833602144</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47313478216903</v>
+        <v>34.2646340776165</v>
       </c>
       <c r="I8" t="n">
-        <v>5.611963833968752</v>
+        <v>3.418446718681097</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683849834533834</v>
+        <v>4.655520934458764</v>
       </c>
       <c r="K8" t="n">
-        <v>12.31060346976124</v>
+        <v>16.63450782475375</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67364734504501</v>
+        <v>42.28081015418457</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81333275115296</v>
+        <v>99.88620731371506</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.60390283073427</v>
+        <v>81.60416660604247</v>
       </c>
       <c r="C9" t="n">
-        <v>41.61439380144718</v>
+        <v>39.74034914176958</v>
       </c>
       <c r="D9" t="n">
-        <v>1.890184112797893</v>
+        <v>1.855177432914472</v>
       </c>
       <c r="E9" t="n">
-        <v>9.847067973684503</v>
+        <v>8.76938394331313</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507831775573552</v>
+        <v>0.7457511260402201</v>
       </c>
       <c r="G9" t="n">
-        <v>29.20227814547836</v>
+        <v>28.4163334753423</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53602616763835</v>
+        <v>34.30455179785012</v>
       </c>
       <c r="I9" t="n">
-        <v>4.68516839384433</v>
+        <v>2.852024292830851</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692394859733469</v>
+        <v>4.660944537751376</v>
       </c>
       <c r="K9" t="n">
-        <v>14.39609716926574</v>
+        <v>18.39583339395753</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83362114501016</v>
+        <v>41.76886061097618</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84411211572308</v>
+        <v>99.90504314670329</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.36695154587082</v>
+        <v>86.19352495554442</v>
       </c>
       <c r="C10" t="n">
-        <v>40.10407995713305</v>
+        <v>42.87841977754996</v>
       </c>
       <c r="D10" t="n">
-        <v>1.789697628507905</v>
+        <v>1.857297242504353</v>
       </c>
       <c r="E10" t="n">
-        <v>9.975310707228175</v>
+        <v>10.57327908202588</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519570524663556</v>
+        <v>0.7466032549851914</v>
       </c>
       <c r="G10" t="n">
-        <v>27.64981865529998</v>
+        <v>29.75023501860034</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59002441345236</v>
+        <v>35.64518148551413</v>
       </c>
       <c r="I10" t="n">
-        <v>3.910411511001316</v>
+        <v>2.954658528257088</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699731577914722</v>
+        <v>4.666270343657446</v>
       </c>
       <c r="K10" t="n">
-        <v>16.63304845412918</v>
+        <v>13.80647504445557</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13272802224209</v>
+        <v>43.2167289694884</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86985643350432</v>
+        <v>99.90162379149393</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.05066877826503</v>
+        <v>86.05512798167675</v>
       </c>
       <c r="C11" t="n">
-        <v>38.39361398575794</v>
+        <v>43.1321611448201</v>
       </c>
       <c r="D11" t="n">
-        <v>1.686783442649508</v>
+        <v>1.847810351513292</v>
       </c>
       <c r="E11" t="n">
-        <v>9.945535265534188</v>
+        <v>10.95903391342345</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529661631855782</v>
+        <v>0.7473287883511283</v>
       </c>
       <c r="G11" t="n">
-        <v>26.05985254554161</v>
+        <v>29.61990302003887</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6364435065366</v>
+        <v>35.70144998983087</v>
       </c>
       <c r="I11" t="n">
-        <v>3.263049334907683</v>
+        <v>2.508796991324592</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706038519909863</v>
+        <v>4.670804927194552</v>
       </c>
       <c r="K11" t="n">
-        <v>18.94933122173496</v>
+        <v>13.94487201832325</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54843225053484</v>
+        <v>42.83942145812392</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89137745802775</v>
+        <v>99.91645462126726</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.49891558220318</v>
+        <v>84.37863669704262</v>
       </c>
       <c r="C12" t="n">
-        <v>36.34658551736398</v>
+        <v>41.84602881526548</v>
       </c>
       <c r="D12" t="n">
-        <v>1.574406425987109</v>
+        <v>1.776261221095314</v>
       </c>
       <c r="E12" t="n">
-        <v>9.73666824661913</v>
+        <v>10.88342081742339</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538365948842282</v>
+        <v>0.7479465217203581</v>
       </c>
       <c r="G12" t="n">
-        <v>24.32369103856712</v>
+        <v>28.47298970049122</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6764833646745</v>
+        <v>35.73096039720761</v>
       </c>
       <c r="I12" t="n">
-        <v>2.722351193444668</v>
+        <v>2.092392278352512</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711478718026425</v>
+        <v>4.674665760752238</v>
       </c>
       <c r="K12" t="n">
-        <v>21.50108441779683</v>
+        <v>15.62136330295736</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0616898055362</v>
+        <v>42.46291907646258</v>
       </c>
       <c r="M12" t="n">
-        <v>99.909359740697</v>
+        <v>99.93031119468543</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.10286887203435</v>
+        <v>85.57268734233281</v>
       </c>
       <c r="C13" t="n">
-        <v>34.37065992831162</v>
+        <v>42.84202132640947</v>
       </c>
       <c r="D13" t="n">
-        <v>1.470005576650844</v>
+        <v>1.777605520326768</v>
       </c>
       <c r="E13" t="n">
-        <v>9.469498074351343</v>
+        <v>11.53462938037435</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545864020650533</v>
+        <v>0.748512578065211</v>
       </c>
       <c r="G13" t="n">
-        <v>22.71075681681612</v>
+        <v>28.81369728607608</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71097449499245</v>
+        <v>36.07716091610298</v>
       </c>
       <c r="I13" t="n">
-        <v>2.270882494251955</v>
+        <v>1.94287804847986</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716165012906583</v>
+        <v>4.678203612907568</v>
       </c>
       <c r="K13" t="n">
-        <v>23.89713112796566</v>
+        <v>14.42731265766717</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65658807723815</v>
+        <v>42.66595239048042</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92437913351543</v>
+        <v>99.93528637455707</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.06245663734414</v>
+        <v>83.84085493961032</v>
       </c>
       <c r="C14" t="n">
-        <v>38.69676966335008</v>
+        <v>41.41245653551989</v>
       </c>
       <c r="D14" t="n">
-        <v>1.471741731830382</v>
+        <v>1.705624586766565</v>
       </c>
       <c r="E14" t="n">
-        <v>11.874430955248</v>
+        <v>11.33757332635551</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554776089496822</v>
+        <v>0.7489947102157114</v>
       </c>
       <c r="G14" t="n">
-        <v>24.6408223212084</v>
+        <v>27.64693851633983</v>
       </c>
       <c r="H14" t="n">
-        <v>36.65521289805157</v>
+        <v>36.10039894801606</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9430360661206</v>
+        <v>1.620107913068431</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721735055935513</v>
+        <v>4.681216938848196</v>
       </c>
       <c r="K14" t="n">
-        <v>16.93754336265584</v>
+        <v>16.15914506038968</v>
       </c>
       <c r="L14" t="n">
-        <v>44.26770149787612</v>
+        <v>42.37442956941042</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90201452388204</v>
+        <v>99.94603116531999</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.22461351158584</v>
+        <v>83.14903696738169</v>
       </c>
       <c r="C15" t="n">
-        <v>38.31338450066157</v>
+        <v>40.95218241977631</v>
       </c>
       <c r="D15" t="n">
-        <v>1.440713334969815</v>
+        <v>1.676565234695061</v>
       </c>
       <c r="E15" t="n">
-        <v>12.03324683703936</v>
+        <v>11.37280062571182</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562294825697365</v>
+        <v>0.7494061706036537</v>
       </c>
       <c r="G15" t="n">
-        <v>24.12132545744664</v>
+        <v>27.17590747804518</v>
       </c>
       <c r="H15" t="n">
-        <v>36.69169324808317</v>
+        <v>36.12023070911321</v>
       </c>
       <c r="I15" t="n">
-        <v>2.454970885416284</v>
+        <v>1.370338182939921</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726434266060853</v>
+        <v>4.683788566272835</v>
       </c>
       <c r="K15" t="n">
-        <v>17.77538648841416</v>
+        <v>16.85096303261832</v>
       </c>
       <c r="L15" t="n">
-        <v>43.82947800908758</v>
+        <v>42.15120168758146</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91824899816331</v>
+        <v>99.95434713997608</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.75355453999663</v>
+        <v>81.05042362235258</v>
       </c>
       <c r="C16" t="n">
-        <v>36.22142431896636</v>
+        <v>39.06639091165715</v>
       </c>
       <c r="D16" t="n">
-        <v>1.347170184658147</v>
+        <v>1.589842953087551</v>
       </c>
       <c r="E16" t="n">
-        <v>11.59320786023038</v>
+        <v>10.97494349546384</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568766533581883</v>
+        <v>0.7497582910520139</v>
       </c>
       <c r="G16" t="n">
-        <v>22.55516741738806</v>
+        <v>25.77020213924914</v>
       </c>
       <c r="H16" t="n">
-        <v>36.72309349443207</v>
+        <v>36.13720237592231</v>
       </c>
       <c r="I16" t="n">
-        <v>2.047559846441099</v>
+        <v>1.142485048502647</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730479083488676</v>
+        <v>4.685989319075086</v>
       </c>
       <c r="K16" t="n">
-        <v>20.24644546000338</v>
+        <v>18.94957637764742</v>
       </c>
       <c r="L16" t="n">
-        <v>43.46393658532426</v>
+        <v>41.94596776116931</v>
       </c>
       <c r="M16" t="n">
-        <v>99.931806364294</v>
+        <v>99.9619350504739</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.44874811839665</v>
+        <v>85.2627888620103</v>
       </c>
       <c r="C17" t="n">
-        <v>37.45933983722873</v>
+        <v>41.82381993497626</v>
       </c>
       <c r="D17" t="n">
-        <v>1.348292582171738</v>
+        <v>1.5906587359035</v>
       </c>
       <c r="E17" t="n">
-        <v>12.37647636356056</v>
+        <v>12.46018969742878</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575072466443961</v>
+        <v>0.7501430082523939</v>
       </c>
       <c r="G17" t="n">
-        <v>23.00827296819729</v>
+        <v>27.04428920027087</v>
       </c>
       <c r="H17" t="n">
-        <v>37.18800308097689</v>
+        <v>37.41660896905858</v>
       </c>
       <c r="I17" t="n">
-        <v>2.035775585318299</v>
+        <v>1.312505449518706</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734420291527474</v>
+        <v>4.688393801577461</v>
       </c>
       <c r="K17" t="n">
-        <v>18.55125188160337</v>
+        <v>14.73721113798972</v>
       </c>
       <c r="L17" t="n">
-        <v>43.92160558494157</v>
+        <v>43.39524118303491</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93219730377366</v>
+        <v>99.95627225600089</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.04633294628833</v>
+        <v>86.85714713370709</v>
       </c>
       <c r="C18" t="n">
-        <v>35.37088059753768</v>
+        <v>42.53045178299229</v>
       </c>
       <c r="D18" t="n">
-        <v>1.26101364502374</v>
+        <v>1.59197230286826</v>
       </c>
       <c r="E18" t="n">
-        <v>11.85825974309748</v>
+        <v>13.04718177643938</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580495512197684</v>
+        <v>0.7507624768110766</v>
       </c>
       <c r="G18" t="n">
-        <v>21.51887991150577</v>
+        <v>27.17565690017626</v>
       </c>
       <c r="H18" t="n">
-        <v>37.21462622459579</v>
+        <v>37.4475076278128</v>
       </c>
       <c r="I18" t="n">
-        <v>1.69769417572224</v>
+        <v>2.1518005695301</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737809695123551</v>
+        <v>4.692265480069228</v>
       </c>
       <c r="K18" t="n">
-        <v>20.95366705371165</v>
+        <v>13.1428528662929</v>
       </c>
       <c r="L18" t="n">
-        <v>43.61890302693628</v>
+        <v>44.25502784813164</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94345067818563</v>
+        <v>99.92833249741683</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.08171673948063</v>
+        <v>84.54975532189286</v>
       </c>
       <c r="C19" t="n">
-        <v>34.66737750177826</v>
+        <v>40.55704283469325</v>
       </c>
       <c r="D19" t="n">
-        <v>1.226637305800535</v>
+        <v>1.505189436871176</v>
       </c>
       <c r="E19" t="n">
-        <v>11.77092652196216</v>
+        <v>12.63501599892998</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758507658902239</v>
+        <v>0.7512936019437776</v>
       </c>
       <c r="G19" t="n">
-        <v>20.93225635000782</v>
+        <v>25.69423578066204</v>
       </c>
       <c r="H19" t="n">
-        <v>37.2371159235163</v>
+        <v>37.47399977822318</v>
       </c>
       <c r="I19" t="n">
-        <v>1.415600111152582</v>
+        <v>1.794435713114089</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740672868138993</v>
+        <v>4.69558501214861</v>
       </c>
       <c r="K19" t="n">
-        <v>21.91828326051935</v>
+        <v>15.45024467810713</v>
       </c>
       <c r="L19" t="n">
-        <v>43.36718106615454</v>
+        <v>43.93294024915711</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95284182845216</v>
+        <v>99.9402277619575</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.59066938463295</v>
+        <v>82.12639947125298</v>
       </c>
       <c r="C20" t="n">
-        <v>32.39389160837403</v>
+        <v>38.41160615014407</v>
       </c>
       <c r="D20" t="n">
-        <v>1.13717204480645</v>
+        <v>1.414478691344368</v>
       </c>
       <c r="E20" t="n">
-        <v>11.10912295138101</v>
+        <v>12.12294106716388</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589024395406262</v>
+        <v>0.7517498657081431</v>
       </c>
       <c r="G20" t="n">
-        <v>19.40555422812319</v>
+        <v>24.14576405590003</v>
       </c>
       <c r="H20" t="n">
-        <v>37.25649673295632</v>
+        <v>37.49675789590235</v>
       </c>
       <c r="I20" t="n">
-        <v>1.180280740696448</v>
+        <v>1.496271234558312</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743140247128912</v>
+        <v>4.698436660675894</v>
       </c>
       <c r="K20" t="n">
-        <v>24.40933061536704</v>
+        <v>17.87360052874701</v>
       </c>
       <c r="L20" t="n">
-        <v>43.15745555094911</v>
+        <v>43.66494788463353</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96067777469018</v>
+        <v>99.95015456352461</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.54236757947359</v>
+        <v>79.70977840986426</v>
       </c>
       <c r="C21" t="n">
-        <v>36.09372882856055</v>
+        <v>36.2261280679719</v>
       </c>
       <c r="D21" t="n">
-        <v>1.137959186748384</v>
+        <v>1.324458842704969</v>
       </c>
       <c r="E21" t="n">
-        <v>13.10068338452312</v>
+        <v>11.55934018334659</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594277461050344</v>
+        <v>0.7521420553296474</v>
       </c>
       <c r="G21" t="n">
-        <v>21.12064231898293</v>
+        <v>22.6090862403234</v>
       </c>
       <c r="H21" t="n">
-        <v>38.98394111204244</v>
+        <v>37.51632004011768</v>
       </c>
       <c r="I21" t="n">
-        <v>1.693290417915227</v>
+        <v>1.24754320223167</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746423413156463</v>
+        <v>4.700887845810295</v>
       </c>
       <c r="K21" t="n">
-        <v>18.45763242052639</v>
+        <v>20.29022159013574</v>
       </c>
       <c r="L21" t="n">
-        <v>45.39223477938769</v>
+        <v>43.44208725204351</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94359602847463</v>
+        <v>99.95843691015115</v>
       </c>
     </row>
   </sheetData>
